--- a/domain_model_comparison_RMS.xlsx
+++ b/domain_model_comparison_RMS.xlsx
@@ -1,27 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\docs\Projects\PythonProject\DMP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\docs\Projects\DMP\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B0185D-BA27-424B-A901-EDE3278EDC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Single Prompt" sheetId="1" r:id="rId1"/>
     <sheet name="Multi Step" sheetId="2" r:id="rId2"/>
     <sheet name="No Few Shot" sheetId="3" r:id="rId3"/>
+    <sheet name="DMP" sheetId="4" r:id="rId4"/>
+    <sheet name="GoldStandard" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="153">
   <si>
     <t>Class Name</t>
   </si>
@@ -210,14 +213,292 @@
   </si>
   <si>
     <t>records</t>
+  </si>
+  <si>
+    <t>ActiveOrder</t>
+  </si>
+  <si>
+    <t>AllergyList</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>ContactInformation</t>
+  </si>
+  <si>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Drink</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>EmployeeInformation</t>
+  </si>
+  <si>
+    <t>EntryTime</t>
+  </si>
+  <si>
+    <t>ExpiryDate</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Ingredient</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>ItemList</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>MonthlyReport</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>OnlineMenu</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>OrderableMenuItem</t>
+  </si>
+  <si>
+    <t>RestaurantEmployee</t>
+  </si>
+  <si>
+    <t>RestaurantManager</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Shift</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Waiter</t>
+  </si>
+  <si>
+    <t>WeeklyReport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cook </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> create </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> give </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> see </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AllergyList</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ingredient</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ExpiryDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> add </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> change </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ItemList</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> delete </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> display </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> edit </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> read </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Employee</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> update </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OnlineMenu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RestaurantEmployee </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ActiveOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RestaurantManager </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> know </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EmployeeInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MonthlyReport</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> WeeklyReport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiter </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OrderableMenuItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ContactInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> enter </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mark </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EntryTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Drink</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Food</t>
+  </si>
+  <si>
+    <t>CurrentStock</t>
+  </si>
+  <si>
+    <t>CustomerOrder</t>
+  </si>
+  <si>
+    <t>Dish</t>
+  </si>
+  <si>
+    <t>EmployeeData</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>OrderedItem</t>
+  </si>
+  <si>
+    <t>StoreOrder</t>
+  </si>
+  <si>
+    <t>givesCommentAbout</t>
+  </si>
+  <si>
+    <t>seesIngredientOf</t>
+  </si>
+  <si>
+    <t>changesShiftOf</t>
+  </si>
+  <si>
+    <t>displays(ByDate)</t>
+  </si>
+  <si>
+    <t>seesCommentsAbout</t>
+  </si>
+  <si>
+    <t>seesCountOf</t>
+  </si>
+  <si>
+    <t>seesRemaining</t>
+  </si>
+  <si>
+    <t>update</t>
+  </si>
+  <si>
+    <t>addsNotesTo</t>
+  </si>
+  <si>
+    <t>edtis</t>
+  </si>
+  <si>
+    <t>enters</t>
+  </si>
+  <si>
+    <t>entersNotesTo</t>
+  </si>
+  <si>
+    <t>seesContentsOf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -233,7 +514,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -241,17 +522,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -548,17 +857,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -572,7 +881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -586,7 +895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -600,7 +909,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -614,7 +923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -628,7 +937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -642,7 +951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -656,7 +965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -670,7 +979,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -684,7 +993,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -698,7 +1007,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -712,7 +1021,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -726,7 +1035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -740,7 +1049,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -754,7 +1063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -768,7 +1077,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -782,7 +1091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -796,7 +1105,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -810,7 +1119,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -824,7 +1133,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -844,17 +1153,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -868,7 +1177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -882,7 +1191,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -896,7 +1205,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -910,7 +1219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -924,7 +1233,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -938,7 +1247,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -952,7 +1261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -966,7 +1275,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -980,7 +1289,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -994,7 +1303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1008,7 +1317,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1022,7 +1331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1036,7 +1345,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1050,7 +1359,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1064,7 +1373,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1078,7 +1387,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1092,7 +1401,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1106,7 +1415,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1120,7 +1429,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1134,7 +1443,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1148,7 +1457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1162,7 +1471,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1176,7 +1485,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -1190,7 +1499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -1204,7 +1513,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1218,7 +1527,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>16</v>
       </c>
@@ -1229,7 +1538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>18</v>
       </c>
@@ -1240,7 +1549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>18</v>
       </c>
@@ -1251,7 +1560,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>18</v>
       </c>
@@ -1262,7 +1571,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>18</v>
       </c>
@@ -1273,7 +1582,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>18</v>
       </c>
@@ -1284,7 +1593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>18</v>
       </c>
@@ -1295,7 +1604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>18</v>
       </c>
@@ -1306,7 +1615,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>18</v>
       </c>
@@ -1317,7 +1626,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>18</v>
       </c>
@@ -1328,7 +1637,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>18</v>
       </c>
@@ -1339,7 +1648,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>18</v>
       </c>
@@ -1350,7 +1659,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>18</v>
       </c>
@@ -1361,7 +1670,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>18</v>
       </c>
@@ -1372,7 +1681,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>18</v>
       </c>
@@ -1383,7 +1692,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>18</v>
       </c>
@@ -1400,17 +1709,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1424,7 +1733,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1438,7 +1747,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1452,7 +1761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1466,7 +1775,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1480,7 +1789,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1494,7 +1803,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1508,7 +1817,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1522,7 +1831,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1536,7 +1845,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1550,7 +1859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1564,7 +1873,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1578,7 +1887,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1592,7 +1901,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1606,7 +1915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1620,7 +1929,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1634,7 +1943,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1648,7 +1957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -1662,7 +1971,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1676,7 +1985,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1690,7 +1999,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1704,7 +2013,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -1718,7 +2027,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1732,7 +2041,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1746,7 +2055,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1760,7 +2069,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1774,7 +2083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -1788,7 +2097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1802,7 +2111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -1816,7 +2125,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>18</v>
       </c>
@@ -1827,7 +2136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>18</v>
       </c>
@@ -1838,7 +2147,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>18</v>
       </c>
@@ -1849,7 +2158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>18</v>
       </c>
@@ -1860,7 +2169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>18</v>
       </c>
@@ -1871,7 +2180,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>18</v>
       </c>
@@ -1882,7 +2191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>18</v>
       </c>
@@ -1893,7 +2202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>18</v>
       </c>
@@ -1904,7 +2213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>18</v>
       </c>
@@ -1915,7 +2224,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>18</v>
       </c>
@@ -1926,7 +2235,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>18</v>
       </c>
@@ -1937,7 +2246,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>18</v>
       </c>
@@ -1948,7 +2257,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>18</v>
       </c>
@@ -1962,4 +2271,1295 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4D1F4E-89C0-45D9-B478-F96295CC078B}">
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C30" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C32" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C33" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C34" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C36" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C38" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C39" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C40" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C41" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C42" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C44" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C45" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C46" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72A0BC-09AF-4D48-B425-758E4E759EA6}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C34" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C41" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C42" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C43" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C44" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C45" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C48" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C49" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C50" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C51" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>